--- a/data/한전_전기요금_2026_HEMS정리.xlsx
+++ b/data/한전_전기요금_2026_HEMS정리.xlsx
@@ -413,7 +413,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -711,6 +711,9 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1075,7 +1078,7 @@
     <row r="2" ht="15" customHeight="1" s="42">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>기준일 2026-09-15 · 셀 색상: 흰색=확정(1차·요금표 근거) / 노랑=추정·산출 / 주황=확인필요 · 출처ID는 '출처' 시트 참조 (A1=약관, A2=시행세칙)</t>
+          <t>기준일 2026-09-16 · 셀 색상: 흰색=확정(1차·요금표 근거) / 노랑=추정·산출 / 주황=확인필요 · 출처ID는 '출처' 시트 참조 (A1=약관, A2=시행세칙)</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="42" min="1" max="1"/>
@@ -3016,7 +3019,7 @@
     <row r="2" ht="46" customHeight="1" s="42">
       <c r="A2" s="98" t="inlineStr">
         <is>
-          <t>근거: 전력시장운영규칙 제12장 수요반응자원의 거래(2026.7.24판, 출처 S35) · 별표26 정산기준 · 별표28 고객기준부하 · 전력거래소 「2025년 12월 수요자원거래시장 현황 및 운영정보」(2026.3 발간, S33) · 전력거래소 2026 사업실명제 내역서(S32) · 한전 선택공급약관 제3장 긴급절전 수요조정(S34). 셀 색상: 흰색=원문 확정 / 노랑=추정·산출 / 주황=확인필요. 핵심: DR 시장은 한전이 아니라 전력거래소(KPX)가 운영하고, 가정은 전력거래소와 직접 거래·정산할 수 없고(전력거래자 등록은 수요관리사업자만 가능, 제12.1.3조·제12.2.1조) 반드시 수요관리사업자(앱)의 고객으로 참여한다. 한전 자체 제도는 긴급절전(대형 사업장)과 에너지캐시백(주택, DR 아님)뿐이다.</t>
+          <t>근거: 전력시장운영규칙 제12장 수요반응자원의 거래(2026.7.24판, 출처 S35) · 별표26 정산기준 · 별표28 고객기준부하 · 전력거래소 「2026년 6월 수요자원거래시장 현황 및 운영정보」(2026.9.9 게시, 참여현황 2026.8월 기준, S39; 이전 2025.12월분 S33) · 전력거래소 2026 사업실명제 내역서(S32) · 한전 선택공급약관 제3장 긴급절전 수요조정(S34). 셀 색상: 흰색=원문 확정 / 노랑=추정·산출 / 주황=확인필요. 핵심: DR 시장은 한전이 아니라 전력거래소(KPX)가 운영하고, 가정은 전력거래소와 직접 거래·정산할 수 없고(전력거래자 등록은 수요관리사업자만 가능, 제12.1.3조·제12.2.1조) 반드시 수요관리사업자(앱)의 고객으로 참여한다. 한전 자체 제도는 긴급절전(대형 사업장)과 에너지캐시백(주택, DR 아님)뿐이다.</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3111,12 @@
       </c>
       <c r="F6" s="96" t="inlineStr">
         <is>
-          <t>국민DR 89,973고객 · 육지 플러스DR 43,061고객 · 제주 플러스DR 1,573고객</t>
+          <t>국민DR 100,789고객 · 육지 플러스DR 42,651고객 · 제주 플러스DR 1,310고객 (2026.8)</t>
         </is>
       </c>
       <c r="G6" s="96" t="inlineStr">
         <is>
-          <t>S35 제12.1.3조 · S33 p.6</t>
+          <t>S35 제12.1.3조 · S39 p.5</t>
         </is>
       </c>
       <c r="H6" s="96" t="inlineStr">
@@ -3150,12 +3153,12 @@
       </c>
       <c r="F7" s="96" t="inlineStr">
         <is>
-          <t>27개 사업자 · 75자원 · 3,877고객 · 4,239MW</t>
+          <t>28개 사업자 · 81자원 · 4,033고객 · 4,326MW / 휴일DR 9자원 · 132고객 · 975MW (2026.8)</t>
         </is>
       </c>
       <c r="G7" s="96" t="inlineStr">
         <is>
-          <t>S35 제12.2.2조 · S33 p.3</t>
+          <t>S35 제12.2.2조 · S39 p.3</t>
         </is>
       </c>
       <c r="H7" s="96" t="inlineStr">
@@ -3794,22 +3797,22 @@
     <row r="23" ht="64" customHeight="1" s="42">
       <c r="A23" s="95" t="inlineStr">
         <is>
-          <t>2025년 단가 (KPX 공표)</t>
+          <t>단가 (KPX 공표)</t>
         </is>
       </c>
       <c r="B23" s="99" t="inlineStr">
         <is>
-          <t>육지 RBP 67,277원/kW (12월 67,253), 제주 76,562원/kW. 실적 평균 ≈ 1,625원/kWh (2025 정산금 12.97억 ÷ 798,187kWh)</t>
+          <t>2026년 RBP 육지 65,760원/kW (1월 65,871), 제주 74,771원/kW — 2025년(67,277/76,562) 대비 약 2% 인하. 실적 평균 2025 ≈ 1,625원/kWh, 2026 상반기 ≈ 1,552원/kWh (10.59억 ÷ 682,625kWh)</t>
         </is>
       </c>
       <c r="C23" s="96" t="inlineStr">
         <is>
-          <t>육지 50원/kWh, 제주 96~97원/kWh</t>
+          <t>육지 50원/kWh. 단, 2026.4.16~ 봄·가을철 공휴일·토요일 및 설·추석 연휴는 별표26 산식으로 61.35원/kWh (규칙 26-긴급4차). 제주 2026.1~5월 96원 → 6월 76원</t>
         </is>
       </c>
       <c r="D23" s="96" t="inlineStr">
         <is>
-          <t>고정기본정산금 2025.12 2,862원/kW-월 (1~12월 862~3,075)</t>
+          <t>고정기본정산금 2026.6 1,952원/kW-월 (2026.1~6: 744~2,650)</t>
         </is>
       </c>
       <c r="E23" s="96" t="inlineStr">
@@ -3819,12 +3822,12 @@
       </c>
       <c r="F23" s="96" t="inlineStr">
         <is>
-          <t>3,526원/kW-월 (1,095~3,835)</t>
+          <t>2,446원/kW-월 (2026.1~6: 907~3,286)</t>
         </is>
       </c>
       <c r="G23" s="96" t="inlineStr">
         <is>
-          <t>598~972원/kW-월 (9~11월)</t>
+          <t>224~972원/kW-월 (2026.2~5)</t>
         </is>
       </c>
       <c r="H23" s="96" t="inlineStr">
@@ -3846,42 +3849,42 @@
     <row r="24" ht="56" customHeight="1" s="42">
       <c r="A24" s="95" t="inlineStr">
         <is>
-          <t>2026.2 참여 현황</t>
+          <t>2026.8 참여 현황</t>
         </is>
       </c>
       <c r="B24" s="96" t="inlineStr">
         <is>
-          <t>12개 사업자 · 214자원 · 89,973고객</t>
+          <t>12개 사업자 · 218자원 · 100,789고객 (2026.2 89,973 → 8월 10만 돌파)</t>
         </is>
       </c>
       <c r="C24" s="96" t="inlineStr">
         <is>
-          <t>육지 10사업자·172자원·43,061고객·2,110MW / 제주 7사업자·26자원·1,573고객</t>
+          <t>육지 10사업자·172자원·42,651고객·2,110MW / 제주 7사업자·25자원·1,310고객</t>
         </is>
       </c>
       <c r="D24" s="96" t="inlineStr">
         <is>
-          <t>수도권 609MW·555고객, 비수도권 3,183MW·1,240고객</t>
+          <t>수도권 609MW·553고객, 비수도권 3,247MW·1,265고객</t>
         </is>
       </c>
       <c r="E24" s="96" t="inlineStr">
         <is>
-          <t>수도권 185MW·753고객, 비수도권 241MW·1,257고객</t>
+          <t>수도권 196MW·828고객, 비수도권 253MW·1,318고객</t>
         </is>
       </c>
       <c r="F24" s="96" t="inlineStr">
         <is>
-          <t>22MW·72고객</t>
+          <t>22MW·69고객</t>
         </is>
       </c>
       <c r="G24" s="96" t="inlineStr">
         <is>
-          <t>(겨울 미운영) 11차 956MW·121고객</t>
+          <t>표준 수도권 142MW·13고객, 비수도권 833MW·119고객 (휴일 합계 975MW·132고객)</t>
         </is>
       </c>
       <c r="H24" s="96" t="inlineStr">
         <is>
-          <t>1단계 639MW·58고객, 3단계 278MW·30고객</t>
+          <t>5단계 체계(2025.4.10~): 1단계 639MW·58고객, 2단계 314MW, 3단계 418MW·32고객, 4단계 255MW, 5단계 333MW</t>
         </is>
       </c>
       <c r="I24" s="96" t="inlineStr">
@@ -3898,22 +3901,22 @@
     <row r="25" ht="56" customHeight="1" s="42">
       <c r="A25" s="95" t="inlineStr">
         <is>
-          <t>2025년 실적</t>
+          <t>실적 (2025 / 2026 상반기)</t>
         </is>
       </c>
       <c r="B25" s="96" t="inlineStr">
         <is>
-          <t>45시간 발령 · 798,187kWh 감축 · 정산금 12.97억원 (누적 2020~25: 304회, 978MWh, 16.1억)</t>
+          <t>2025: 45시간 · 798,187kWh · 12.97억원 / 2026 1~6월: 38시간 · 682,625kWh · 10.59억원 (누적 2020~26.6: 344회, 1,661MWh, 26.7억)</t>
         </is>
       </c>
       <c r="C25" s="96" t="inlineStr">
         <is>
-          <t>육지: 16일 63시간 30,725MWh 13.1억원 (3~6월). 제주: 표에 2023년까지만 수록</t>
+          <t>육지 2025: 16일 63시간 30,725MWh 13.1억 → 2026 3~6월: 26일 104시간 47,561MWh 21.6억 (전년 대비 1.7배). 제주: 2023 이후 표 미수록</t>
         </is>
       </c>
       <c r="D25" s="96" t="inlineStr">
         <is>
-          <t>자발적DR 연간 낙찰 15만MWh대, 신뢰성 감축시험 4,209~4,945MWh/회</t>
+          <t>자발적DR 2026 1~6월 낙찰 6,963~17,899MWh/월, 감축 10,735~25,612MWh/월. 미세먼지DR은 규칙 26-정기1차로 폐지</t>
         </is>
       </c>
       <c r="E25" s="96" t="inlineStr"/>
@@ -4046,7 +4049,7 @@
     <row r="28" ht="40" customHeight="1" s="42">
       <c r="A28" s="97" t="inlineStr">
         <is>
-          <t>"2025년 단가" 행의 국민DR 평균 1,625원/kWh는 KPX 연간 정산금÷감축량으로 역산한 값(노랑)이다. 실제 고객이 받는 금액은 수요관리사업자가 이 정산금에서 운영비를 떼고 배분하므로 더 작다(사업자 계약별, 공통값 없음). 2026년 RBP·MRT는 KPX가 매월 공표하는 현황 보고서로 갱신할 것.</t>
+          <t>"단가" 행의 국민DR 평균(2025 1,625 / 2026 상반기 1,552원/kWh)는 KPX 연간 정산금÷감축량으로 역산한 값(노랑)이다. 실제 고객이 받는 금액은 수요관리사업자가 이 정산금에서 운영비를 떼고 배분하므로 더 작다(사업자 계약별, 공통값 없음). 2026년 RBP·MRT는 KPX가 매월 공표하는 현황 보고서로 갱신할 것.</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4303,7 @@
       </c>
       <c r="B41" s="99" t="inlineStr">
         <is>
-          <t>2025년: 1,297,300천원 ÷ 798,187kWh ≈ 1,625원/kWh. 2025.12.17 18시 발령: 22,221kWh → 34,369천원(1,547원/kWh). 2025.12.29 11시: 13,039kWh → 20,136천원</t>
+          <t>2025년: 1,297,300천원 ÷ 798,187kWh ≈ 1,625원/kWh. 2026년 1~6월: 1,059,100천원 ÷ 682,625kWh ≈ 1,552원/kWh (RBP 인하 반영). 2026.6.29 19시 발령: 24,290kWh → 37,146천원(1,529원/kWh)</t>
         </is>
       </c>
       <c r="C41" s="96" t="inlineStr">
@@ -4344,12 +4347,12 @@
       </c>
       <c r="B43" s="96" t="inlineStr">
         <is>
-          <t>45시간 발령, 798,187kWh, 정산금 12.97억원. 참여고객 2025.12 85,011 → 2026.2 89,973 (12개 사업자, 214자원). 2020~2025 누적 304회·978MWh·16.1억원</t>
+          <t>2025: 45시간, 798,187kWh, 12.97억원. 2026 1~6월: 38시간, 682,625kWh, 10.59억원. 참여고객 2025.12 85,011 → 2026.2 89,973 → 2026.8 100,789 (12개 사업자, 218자원)</t>
         </is>
       </c>
       <c r="C43" s="96" t="inlineStr">
         <is>
-          <t>S33 p.6·p.19</t>
+          <t>S39 p.5·6·17·18</t>
         </is>
       </c>
       <c r="D43" s="96" t="inlineStr">
@@ -4515,17 +4518,17 @@
     <row r="52" ht="28" customHeight="1" s="42">
       <c r="A52" s="95" t="inlineStr">
         <is>
-          <t>정산 단가 (2025)</t>
+          <t>정산 단가 (2025 → 2026)</t>
         </is>
       </c>
       <c r="B52" s="96" t="inlineStr">
         <is>
-          <t>육지 50원/kWh (1~12월 동일), 제주 95~97원/kWh. 증대량 × 단가</t>
+          <t>육지 50원/kWh (2025 연중, 2026 평일). 2026.4.16부터 봄·가을철 공휴일·토요일 및 설·추석 연휴는 별표26 산식 61.35원/kWh(규칙 26-긴급4차). 제주 2025 95~97 → 2026.1~5월 96 → 6월 76원/kWh. 증대량 × 단가</t>
         </is>
       </c>
       <c r="C52" s="96" t="inlineStr">
         <is>
-          <t>S33 p.11</t>
+          <t>S39 p.10</t>
         </is>
       </c>
       <c r="D52" s="96" t="inlineStr">
@@ -4537,17 +4540,17 @@
     <row r="53" ht="40" customHeight="1" s="42">
       <c r="A53" s="95" t="inlineStr">
         <is>
-          <t>2025 실적</t>
+          <t>실적 (2025 → 2026 상반기)</t>
         </is>
       </c>
       <c r="B53" s="96" t="inlineStr">
         <is>
-          <t>육지: 3~6월 16일 63시간 30,725MWh, 정산금 13.1억원 (2024: 10일 21시간 7,187MWh 3.2억). 2025.7 이후·12월 실적 없음. 참여고객 육지 43,061 / 제주 1,573 (2026.2), 육지 증대가능용량 2,110MW</t>
+          <t>육지 2025: 3~6월 16일 63시간 30,725MWh 13.1억. 2026: 3월 4일13h 7,085MWh, 4월 7일33h 19,409MWh, 5월 10일42h 15,481MWh, 6월 5일16h 5,586MWh = 26일 104시간 47,561MWh 21.6억 (2026.6 발령 예: 6/1 11~15시, 6/13 11~14시, 6/14 12~14시, 6/28 11~13시 — 주말 낮 집중). 참여고객 육지 42,651 / 제주 1,310 (2026.8), 육지 증대가능용량 2,110MW</t>
         </is>
       </c>
       <c r="C53" s="96" t="inlineStr">
         <is>
-          <t>S33 p.6·p.20</t>
+          <t>S39 p.5·17·19</t>
         </is>
       </c>
       <c r="D53" s="96" t="inlineStr">
@@ -4806,17 +4809,17 @@
       </c>
       <c r="B67" s="96" t="inlineStr">
         <is>
-          <t>수도권/비수도권 자원. RBP 67,277원/kW(2025)</t>
+          <t>수도권/비수도권 자원. RBP 65,760원/kW (2026, 2025는 67,277)</t>
         </is>
       </c>
       <c r="C67" s="96" t="inlineStr">
         <is>
-          <t>제주권 자원. RBP 76,562원/kW(2025) — 육지보다 14% 높음</t>
+          <t>제주권 자원. RBP 74,771원/kW (2026) — 육지보다 14% 높음</t>
         </is>
       </c>
       <c r="D67" s="96" t="inlineStr">
         <is>
-          <t>S33 p.11</t>
+          <t>S39 p.10</t>
         </is>
       </c>
     </row>
@@ -4828,17 +4831,17 @@
       </c>
       <c r="B68" s="96" t="inlineStr">
         <is>
-          <t>2024.3.28 신설. 증대필요량 = 태양광이용률·수요구간 기준(KPX 매월 공지). 50원/kWh. 43,061고객</t>
+          <t>2024.3.28 신설. 증대필요량 = 태양광이용률·수요구간 기준(KPX 매월 공지). 평일 50원/kWh, 봄·가을 휴일·명절 61.35원/kWh(2026.4.16~). 42,651고객. 2026 상반기 104시간 발령</t>
         </is>
       </c>
       <c r="C68" s="96" t="inlineStr">
         <is>
-          <t>2021.1 신설, 2022.5 시장 분리. 출력제어량 기준 낙찰, 실시간(당일) 시장 병행. 95~97원/kWh. 1,573고객</t>
+          <t>2021.1 신설, 2022.5 시장 분리. 출력제어량 기준 낙찰, 실시간(당일) 시장 병행. 2026 96 → 6월 76원/kWh. 1,310고객</t>
         </is>
       </c>
       <c r="D68" s="96" t="inlineStr">
         <is>
-          <t>S35 제12.7.3.6~3.8조, S33</t>
+          <t>S35 제12.7.3.6~3.8조, S39</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4875,7 @@
       </c>
       <c r="B70" s="99" t="inlineStr">
         <is>
-          <t>국민DR + 플러스DR 둘 다 가능. 플러스DR 단가가 낮아 EV·ESS가 있어야 의미</t>
+          <t>국민DR + 플러스DR 둘 다 가능. 플러스DR은 2026년 봄·가을 주말 낮에 집중 발령(104시간)되고 휴일 단가 61.35원이라 EV·ESS 있는 가정은 주말 낮 충전 스케줄과 결합 가치 있음</t>
         </is>
       </c>
       <c r="C70" s="99" t="inlineStr">
@@ -4960,7 +4963,7 @@
       </c>
       <c r="B75" s="99" t="inlineStr">
         <is>
-          <t>가정이 1시간에 1kWh 줄이면 KPX 정산 ≈ 1,600원(2025 평균). 연 45시간 전부 참여·매회 1kWh 감축 시 KPX 정산 ≈ 7만원, 사업자 배분 후 가정 수령은 그 일부. 감축량을 키우려면 히트펌프·EV·온수기 같은 큰 부하가 있어야 함</t>
+          <t>가정이 1시간에 1kWh 줄이면 KPX 정산 ≈ 1,550~1,600원(2025 1,625 / 2026 상반기 1,552). 연 40~45시간 전부 참여·매회 1kWh 감축 시 KPX 정산 ≈ 6~7만원, 사업자 배분 후 가정 수령은 그 일부</t>
         </is>
       </c>
       <c r="C75" s="96" t="inlineStr">
@@ -4982,7 +4985,7 @@
       </c>
       <c r="B76" s="99" t="inlineStr">
         <is>
-          <t>EV 30kWh 충전을 잉여 시간으로 옮기면 육지 50원 × 30 = 1,500원/회, 제주 96원 × 30 = 2,880원/회 (KPX 정산 기준). 2025 육지 발령 63시간이므로 연 수만 원 규모. 요금 측면 이득(경부하·주말 할인)이 DR 정산보다 큼</t>
+          <t>EV 30kWh 충전을 잉여 시간으로 옮기면 육지 평일 50원 × 30 = 1,500원/회, 봄·가을 휴일 61.35 × 30 = 1,841원/회, 제주 76~96원 × 30 = 2,280~2,880원/회 (KPX 정산 기준). 2026 상반기 육지 발령 104시간이므로 연 수만 원 규모. 요금 측면 이득이 DR 정산보다 큼</t>
         </is>
       </c>
       <c r="C76" s="96" t="inlineStr">
@@ -5026,7 +5029,7 @@
       </c>
       <c r="B78" s="100" t="inlineStr">
         <is>
-          <t>2026년 RBP·MRT·플러스DR 단가(KPX 월간 현황 보고서), 사업자별 고객 배분율·보상 방식, 국민DR 일일 발령 한도·기온 기준 조항 개정 여부, 제주 플러스DR 2024~2025 실적(보고서 표 미수록)</t>
+          <t>2026 하반기 RBP·MRT(KPX 월간 현황 보고서로 매월 갱신), 사업자별 고객 배분율·보상 방식, 제주 플러스DR 2024~2026 실적(보고서 표 미수록), 61.35원 적용 산식(별표26) 원문</t>
         </is>
       </c>
       <c r="C78" s="96" t="inlineStr">
@@ -5040,8 +5043,487 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="92" t="inlineStr">
+        <is>
+          <t>H. 현황판 키값 (scripts/extract.py가 읽어 현황판에 표시 — 키 이름 변경 금지, 값만 갱신)</t>
+        </is>
+      </c>
+      <c r="B80" s="93" t="n"/>
+      <c r="C80" s="93" t="n"/>
+      <c r="D80" s="93" t="n"/>
+      <c r="E80" s="93" t="n"/>
+      <c r="F80" s="93" t="n"/>
+      <c r="G80" s="93" t="n"/>
+      <c r="H80" s="93" t="n"/>
+      <c r="I80" s="93" t="n"/>
+      <c r="J80" s="93" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="104" t="inlineStr">
+        <is>
+          <t>키</t>
+        </is>
+      </c>
+      <c r="B81" s="104" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C81" s="104" t="inlineStr">
+        <is>
+          <t>단위·설명</t>
+        </is>
+      </c>
+      <c r="D81" s="104" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="E81" s="104" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="95" t="inlineStr">
+        <is>
+          <t>기준월</t>
+        </is>
+      </c>
+      <c r="B82" s="96" t="inlineStr">
+        <is>
+          <t>2026.8</t>
+        </is>
+      </c>
+      <c r="C82" s="96" t="inlineStr">
+        <is>
+          <t>KPX 보고서의 참여현황 기준월</t>
+        </is>
+      </c>
+      <c r="D82" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.5</t>
+        </is>
+      </c>
+      <c r="E82" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="95" t="inlineStr">
+        <is>
+          <t>국민DR_참여고객</t>
+        </is>
+      </c>
+      <c r="B83" s="96" t="n">
+        <v>100789</v>
+      </c>
+      <c r="C83" s="96" t="inlineStr">
+        <is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="D83" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.5</t>
+        </is>
+      </c>
+      <c r="E83" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="95" t="inlineStr">
+        <is>
+          <t>국민DR_사업자</t>
+        </is>
+      </c>
+      <c r="B84" s="96" t="n">
+        <v>12</v>
+      </c>
+      <c r="C84" s="96" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="D84" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.5</t>
+        </is>
+      </c>
+      <c r="E84" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="95" t="inlineStr">
+        <is>
+          <t>국민DR_자원</t>
+        </is>
+      </c>
+      <c r="B85" s="96" t="n">
+        <v>218</v>
+      </c>
+      <c r="C85" s="96" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="D85" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.5</t>
+        </is>
+      </c>
+      <c r="E85" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="95" t="inlineStr">
+        <is>
+          <t>국민DR_RBP_육지</t>
+        </is>
+      </c>
+      <c r="B86" s="96" t="n">
+        <v>65760</v>
+      </c>
+      <c r="C86" s="96" t="inlineStr">
+        <is>
+          <t>원/kW (2026)</t>
+        </is>
+      </c>
+      <c r="D86" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.10</t>
+        </is>
+      </c>
+      <c r="E86" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="95" t="inlineStr">
+        <is>
+          <t>국민DR_RBP_제주</t>
+        </is>
+      </c>
+      <c r="B87" s="96" t="n">
+        <v>74771</v>
+      </c>
+      <c r="C87" s="96" t="inlineStr">
+        <is>
+          <t>원/kW (2026)</t>
+        </is>
+      </c>
+      <c r="D87" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.10</t>
+        </is>
+      </c>
+      <c r="E87" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="95" t="inlineStr">
+        <is>
+          <t>국민DR_실적평균단가</t>
+        </is>
+      </c>
+      <c r="B88" s="99" t="n">
+        <v>1552</v>
+      </c>
+      <c r="C88" s="96" t="inlineStr">
+        <is>
+          <t>원/kWh (2026 상반기 역산)</t>
+        </is>
+      </c>
+      <c r="D88" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.18</t>
+        </is>
+      </c>
+      <c r="E88" s="96" t="inlineStr">
+        <is>
+          <t>추정(계산식 병기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="95" t="inlineStr">
+        <is>
+          <t>국민DR_실적문구</t>
+        </is>
+      </c>
+      <c r="B89" s="96" t="inlineStr">
+        <is>
+          <t>2026 1~6월 38시간 · 683MWh (2025 45시간 · 798MWh)</t>
+        </is>
+      </c>
+      <c r="C89" s="96" t="inlineStr">
+        <is>
+          <t>현황판 표시용</t>
+        </is>
+      </c>
+      <c r="D89" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.18</t>
+        </is>
+      </c>
+      <c r="E89" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="95" t="inlineStr">
+        <is>
+          <t>플러스DR_단가_육지_평일</t>
+        </is>
+      </c>
+      <c r="B90" s="96" t="n">
+        <v>50</v>
+      </c>
+      <c r="C90" s="96" t="inlineStr">
+        <is>
+          <t>원/kWh</t>
+        </is>
+      </c>
+      <c r="D90" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.10</t>
+        </is>
+      </c>
+      <c r="E90" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="95" t="inlineStr">
+        <is>
+          <t>플러스DR_단가_육지_휴일</t>
+        </is>
+      </c>
+      <c r="B91" s="96" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="C91" s="96" t="inlineStr">
+        <is>
+          <t>원/kWh (2026.4.16~ 봄·가을 공휴일·토요일·설·추석)</t>
+        </is>
+      </c>
+      <c r="D91" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.10</t>
+        </is>
+      </c>
+      <c r="E91" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="95" t="inlineStr">
+        <is>
+          <t>플러스DR_단가_제주</t>
+        </is>
+      </c>
+      <c r="B92" s="96" t="n">
+        <v>76</v>
+      </c>
+      <c r="C92" s="96" t="inlineStr">
+        <is>
+          <t>원/kWh (2026.6; 1~5월 96)</t>
+        </is>
+      </c>
+      <c r="D92" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.10</t>
+        </is>
+      </c>
+      <c r="E92" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="95" t="inlineStr">
+        <is>
+          <t>플러스DR_고객_육지</t>
+        </is>
+      </c>
+      <c r="B93" s="96" t="n">
+        <v>42651</v>
+      </c>
+      <c r="C93" s="96" t="inlineStr">
+        <is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="D93" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.5</t>
+        </is>
+      </c>
+      <c r="E93" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="95" t="inlineStr">
+        <is>
+          <t>플러스DR_고객_제주</t>
+        </is>
+      </c>
+      <c r="B94" s="96" t="n">
+        <v>1310</v>
+      </c>
+      <c r="C94" s="96" t="inlineStr">
+        <is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="D94" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.5</t>
+        </is>
+      </c>
+      <c r="E94" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="95" t="inlineStr">
+        <is>
+          <t>플러스DR_용량_육지</t>
+        </is>
+      </c>
+      <c r="B95" s="96" t="n">
+        <v>2110</v>
+      </c>
+      <c r="C95" s="96" t="inlineStr">
+        <is>
+          <t>MW (증대가능용량)</t>
+        </is>
+      </c>
+      <c r="D95" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.5</t>
+        </is>
+      </c>
+      <c r="E95" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="95" t="inlineStr">
+        <is>
+          <t>플러스DR_실적문구_육지</t>
+        </is>
+      </c>
+      <c r="B96" s="96" t="inlineStr">
+        <is>
+          <t>2026 3~6월 26일 104시간 47,561MWh (2025 63시간)</t>
+        </is>
+      </c>
+      <c r="C96" s="96" t="inlineStr">
+        <is>
+          <t>현황판 표시용</t>
+        </is>
+      </c>
+      <c r="D96" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.19</t>
+        </is>
+      </c>
+      <c r="E96" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="95" t="inlineStr">
+        <is>
+          <t>플러스DR_실적문구_제주</t>
+        </is>
+      </c>
+      <c r="B97" s="100" t="inlineStr">
+        <is>
+          <t>2023 이후 보고서 표 미수록</t>
+        </is>
+      </c>
+      <c r="C97" s="96" t="inlineStr">
+        <is>
+          <t>현황판 표시용</t>
+        </is>
+      </c>
+      <c r="D97" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.20</t>
+        </is>
+      </c>
+      <c r="E97" s="96" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="95" t="inlineStr">
+        <is>
+          <t>사업장DR_요약</t>
+        </is>
+      </c>
+      <c r="B98" s="96" t="inlineStr">
+        <is>
+          <t>28사업자 · 81자원 · 4,033고객 · 4,326MW / 휴일DR 975MW·132고객</t>
+        </is>
+      </c>
+      <c r="C98" s="96" t="inlineStr">
+        <is>
+          <t>현황판 표시용</t>
+        </is>
+      </c>
+      <c r="D98" s="96" t="inlineStr">
+        <is>
+          <t>S39 p.3</t>
+        </is>
+      </c>
+      <c r="E98" s="96" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="A80:J80"/>
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A12:J12"/>
@@ -5470,7 +5952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="41" min="1" max="1"/>
@@ -6804,6 +7286,38 @@
       <c r="F44" s="85" t="inlineStr">
         <is>
           <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=273132</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1" s="42">
+      <c r="A45" s="82" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="B45" s="83" t="inlineStr">
+        <is>
+          <t>2026년 6월 수요자원거래시장 현황 및 운영정보 (2026.9.9 게시; 참여현황 2026.8월, 단가 2026.1~6월, 실적 2026.6월·누적)</t>
+        </is>
+      </c>
+      <c r="C45" s="84" t="inlineStr">
+        <is>
+          <t>전력거래소</t>
+        </is>
+      </c>
+      <c r="D45" s="82" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E45" s="82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F45" s="85" t="inlineStr">
+        <is>
+          <t>https://kpx.or.kr/board.es?mid=a10102000000&amp;bid=0088&amp;act=view&amp;list_no=78099 (evidence/KPX_2026-06_수요자원시장현황.pdf)</t>
         </is>
       </c>
     </row>
@@ -6854,7 +7368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="42" min="1" max="1"/>
@@ -6881,7 +7395,7 @@
       </c>
       <c r="C1" s="101" t="inlineStr">
         <is>
-          <t>v12</t>
+          <t>v13</t>
         </is>
       </c>
       <c r="D1" s="91" t="inlineStr">
@@ -6891,7 +7405,7 @@
       </c>
       <c r="E1" s="101" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -7171,6 +7685,1698 @@
       <c r="G21" s="103" t="n"/>
       <c r="H21" s="103" t="n"/>
       <c r="I21" s="103" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1" s="42">
+      <c r="A22" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B22" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C22" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!F6</t>
+        </is>
+      </c>
+      <c r="D22" s="96" t="inlineStr">
+        <is>
+          <t>국민DR 89,973고객 · 육지 플러스DR 43,061고객 · 제주 플러스DR 1,573고객</t>
+        </is>
+      </c>
+      <c r="E22" s="96" t="inlineStr">
+        <is>
+          <t>국민DR 100,789고객 · 육지 플러스DR 42,651고객 · 제주 플러스DR 1,310고객 (2026.8)</t>
+        </is>
+      </c>
+      <c r="F22" s="96" t="inlineStr">
+        <is>
+          <t>참여현황 갱신</t>
+        </is>
+      </c>
+      <c r="G22" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H22" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I22" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1" s="42">
+      <c r="A23" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B23" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C23" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!F7</t>
+        </is>
+      </c>
+      <c r="D23" s="96" t="inlineStr">
+        <is>
+          <t>27개 사업자 · 75자원 · 3,877고객 · 4,239MW</t>
+        </is>
+      </c>
+      <c r="E23" s="96" t="inlineStr">
+        <is>
+          <t>28개 사업자 · 81자원 · 4,033고객 · 4,326MW / 휴일DR 9자원 · 132고객 · 975MW (2026.8)</t>
+        </is>
+      </c>
+      <c r="F23" s="96" t="inlineStr">
+        <is>
+          <t>참여현황 갱신</t>
+        </is>
+      </c>
+      <c r="G23" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H23" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I23" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1" s="42">
+      <c r="A24" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B24" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C24" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!A23</t>
+        </is>
+      </c>
+      <c r="D24" s="96" t="inlineStr">
+        <is>
+          <t>2025년 단가 (KPX 공표)</t>
+        </is>
+      </c>
+      <c r="E24" s="96" t="inlineStr">
+        <is>
+          <t>단가 (KPX 공표)</t>
+        </is>
+      </c>
+      <c r="F24" s="96" t="inlineStr">
+        <is>
+          <t>연도 갱신</t>
+        </is>
+      </c>
+      <c r="G24" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H24" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I24" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1" s="42">
+      <c r="A25" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B25" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C25" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B23</t>
+        </is>
+      </c>
+      <c r="D25" s="96" t="inlineStr">
+        <is>
+          <t>육지 RBP 67,277원/kW (12월 67,253), 제주 76,562원/kW. 실적 평균 ≈ 1,625원/kWh (2025 정산금 12.97억 ÷ 798,187kWh)</t>
+        </is>
+      </c>
+      <c r="E25" s="96" t="inlineStr">
+        <is>
+          <t>2026년 RBP 육지 65,760원/kW (1월 65,871), 제주 74,771원/kW — 2025년(67,277/76,562) 대비 약 2% 인하. 실적 평균 2025 ≈ 1,625원/kWh, 2026 상반기 ≈ 1,552원/kWh (10.59억 ÷ 682,625kWh)</t>
+        </is>
+      </c>
+      <c r="F25" s="96" t="inlineStr">
+        <is>
+          <t>2026 단가 반영</t>
+        </is>
+      </c>
+      <c r="G25" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H25" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I25" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1" s="42">
+      <c r="A26" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B26" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C26" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!C23</t>
+        </is>
+      </c>
+      <c r="D26" s="96" t="inlineStr">
+        <is>
+          <t>육지 50원/kWh, 제주 96~97원/kWh</t>
+        </is>
+      </c>
+      <c r="E26" s="96" t="inlineStr">
+        <is>
+          <t>육지 50원/kWh. 단, 2026.4.16~ 봄·가을철 공휴일·토요일 및 설·추석 연휴는 별표26 산식으로 61.35원/kWh (규칙 26-긴급4차). 제주 2026.1~5월 96원 → 6월 76원</t>
+        </is>
+      </c>
+      <c r="F26" s="96" t="inlineStr">
+        <is>
+          <t>휴일 단가 61.35 신설</t>
+        </is>
+      </c>
+      <c r="G26" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H26" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I26" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1" s="42">
+      <c r="A27" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B27" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C27" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!D23</t>
+        </is>
+      </c>
+      <c r="D27" s="96" t="inlineStr">
+        <is>
+          <t>고정기본정산금 2025.12 2,862원/kW-월 (1~12월 862~3,075)</t>
+        </is>
+      </c>
+      <c r="E27" s="96" t="inlineStr">
+        <is>
+          <t>고정기본정산금 2026.6 1,952원/kW-월 (2026.1~6: 744~2,650)</t>
+        </is>
+      </c>
+      <c r="F27" s="96" t="inlineStr">
+        <is>
+          <t>2026 단가</t>
+        </is>
+      </c>
+      <c r="G27" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H27" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I27" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1" s="42">
+      <c r="A28" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B28" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C28" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!F23</t>
+        </is>
+      </c>
+      <c r="D28" s="96" t="inlineStr">
+        <is>
+          <t>3,526원/kW-월 (1,095~3,835)</t>
+        </is>
+      </c>
+      <c r="E28" s="96" t="inlineStr">
+        <is>
+          <t>2,446원/kW-월 (2026.1~6: 907~3,286)</t>
+        </is>
+      </c>
+      <c r="F28" s="96" t="inlineStr">
+        <is>
+          <t>2026 단가</t>
+        </is>
+      </c>
+      <c r="G28" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H28" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I28" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1" s="42">
+      <c r="A29" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B29" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C29" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!G23</t>
+        </is>
+      </c>
+      <c r="D29" s="96" t="inlineStr">
+        <is>
+          <t>598~972원/kW-월 (9~11월)</t>
+        </is>
+      </c>
+      <c r="E29" s="96" t="inlineStr">
+        <is>
+          <t>224~972원/kW-월 (2026.2~5)</t>
+        </is>
+      </c>
+      <c r="F29" s="96" t="inlineStr">
+        <is>
+          <t>2026 단가</t>
+        </is>
+      </c>
+      <c r="G29" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H29" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I29" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1" s="42">
+      <c r="A30" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B30" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C30" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!A24</t>
+        </is>
+      </c>
+      <c r="D30" s="96" t="inlineStr">
+        <is>
+          <t>2026.2 참여 현황</t>
+        </is>
+      </c>
+      <c r="E30" s="96" t="inlineStr">
+        <is>
+          <t>2026.8 참여 현황</t>
+        </is>
+      </c>
+      <c r="F30" s="96" t="inlineStr">
+        <is>
+          <t>기준월 갱신</t>
+        </is>
+      </c>
+      <c r="G30" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H30" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I30" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1" s="42">
+      <c r="A31" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B31" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C31" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B24</t>
+        </is>
+      </c>
+      <c r="D31" s="96" t="inlineStr">
+        <is>
+          <t>12개 사업자 · 214자원 · 89,973고객</t>
+        </is>
+      </c>
+      <c r="E31" s="96" t="inlineStr">
+        <is>
+          <t>12개 사업자 · 218자원 · 100,789고객 (2026.2 89,973 → 8월 10만 돌파)</t>
+        </is>
+      </c>
+      <c r="F31" s="96" t="inlineStr">
+        <is>
+          <t>참여현황</t>
+        </is>
+      </c>
+      <c r="G31" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H31" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I31" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1" s="42">
+      <c r="A32" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B32" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C32" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!C24</t>
+        </is>
+      </c>
+      <c r="D32" s="96" t="inlineStr">
+        <is>
+          <t>육지 10사업자·172자원·43,061고객·2,110MW / 제주 7사업자·26자원·1,573고객</t>
+        </is>
+      </c>
+      <c r="E32" s="96" t="inlineStr">
+        <is>
+          <t>육지 10사업자·172자원·42,651고객·2,110MW / 제주 7사업자·25자원·1,310고객</t>
+        </is>
+      </c>
+      <c r="F32" s="96" t="inlineStr">
+        <is>
+          <t>참여현황</t>
+        </is>
+      </c>
+      <c r="G32" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H32" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I32" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1" s="42">
+      <c r="A33" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B33" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C33" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!D24</t>
+        </is>
+      </c>
+      <c r="D33" s="96" t="inlineStr">
+        <is>
+          <t>수도권 609MW·555고객, 비수도권 3,183MW·1,240고객</t>
+        </is>
+      </c>
+      <c r="E33" s="96" t="inlineStr">
+        <is>
+          <t>수도권 609MW·553고객, 비수도권 3,247MW·1,265고객</t>
+        </is>
+      </c>
+      <c r="F33" s="96" t="inlineStr">
+        <is>
+          <t>참여현황</t>
+        </is>
+      </c>
+      <c r="G33" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H33" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I33" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1" s="42">
+      <c r="A34" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B34" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C34" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!E24</t>
+        </is>
+      </c>
+      <c r="D34" s="96" t="inlineStr">
+        <is>
+          <t>수도권 185MW·753고객, 비수도권 241MW·1,257고객</t>
+        </is>
+      </c>
+      <c r="E34" s="96" t="inlineStr">
+        <is>
+          <t>수도권 196MW·828고객, 비수도권 253MW·1,318고객</t>
+        </is>
+      </c>
+      <c r="F34" s="96" t="inlineStr">
+        <is>
+          <t>참여현황</t>
+        </is>
+      </c>
+      <c r="G34" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H34" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I34" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1" s="42">
+      <c r="A35" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B35" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C35" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!F24</t>
+        </is>
+      </c>
+      <c r="D35" s="96" t="inlineStr">
+        <is>
+          <t>22MW·72고객</t>
+        </is>
+      </c>
+      <c r="E35" s="96" t="inlineStr">
+        <is>
+          <t>22MW·69고객</t>
+        </is>
+      </c>
+      <c r="F35" s="96" t="inlineStr">
+        <is>
+          <t>참여현황</t>
+        </is>
+      </c>
+      <c r="G35" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H35" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I35" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1" s="42">
+      <c r="A36" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B36" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C36" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!G24</t>
+        </is>
+      </c>
+      <c r="D36" s="96" t="inlineStr">
+        <is>
+          <t>(겨울 미운영) 11차 956MW·121고객</t>
+        </is>
+      </c>
+      <c r="E36" s="96" t="inlineStr">
+        <is>
+          <t>표준 수도권 142MW·13고객, 비수도권 833MW·119고객 (휴일 합계 975MW·132고객)</t>
+        </is>
+      </c>
+      <c r="F36" s="96" t="inlineStr">
+        <is>
+          <t>참여현황</t>
+        </is>
+      </c>
+      <c r="G36" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H36" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I36" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1" s="42">
+      <c r="A37" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B37" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C37" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!H24</t>
+        </is>
+      </c>
+      <c r="D37" s="96" t="inlineStr">
+        <is>
+          <t>1단계 639MW·58고객, 3단계 278MW·30고객</t>
+        </is>
+      </c>
+      <c r="E37" s="96" t="inlineStr">
+        <is>
+          <t>5단계 체계(2025.4.10~): 1단계 639MW·58고객, 2단계 314MW, 3단계 418MW·32고객, 4단계 255MW, 5단계 333MW</t>
+        </is>
+      </c>
+      <c r="F37" s="96" t="inlineStr">
+        <is>
+          <t>참여현황</t>
+        </is>
+      </c>
+      <c r="G37" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H37" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I37" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1" s="42">
+      <c r="A38" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B38" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C38" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!A25</t>
+        </is>
+      </c>
+      <c r="D38" s="96" t="inlineStr">
+        <is>
+          <t>2025년 실적</t>
+        </is>
+      </c>
+      <c r="E38" s="96" t="inlineStr">
+        <is>
+          <t>실적 (2025 / 2026 상반기)</t>
+        </is>
+      </c>
+      <c r="F38" s="96" t="inlineStr">
+        <is>
+          <t>연도 갱신</t>
+        </is>
+      </c>
+      <c r="G38" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H38" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I38" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1" s="42">
+      <c r="A39" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B39" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C39" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B25</t>
+        </is>
+      </c>
+      <c r="D39" s="96" t="inlineStr">
+        <is>
+          <t>45시간 발령 · 798,187kWh 감축 · 정산금 12.97억원 (누적 2020~25: 304회, 978MWh, 16.1억)</t>
+        </is>
+      </c>
+      <c r="E39" s="96" t="inlineStr">
+        <is>
+          <t>2025: 45시간 · 798,187kWh · 12.97억원 / 2026 1~6월: 38시간 · 682,625kWh · 10.59억원 (누적 2020~26.6: 344회, 1,661MWh, 26.7억)</t>
+        </is>
+      </c>
+      <c r="F39" s="96" t="inlineStr">
+        <is>
+          <t>2026 실적</t>
+        </is>
+      </c>
+      <c r="G39" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H39" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I39" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1" s="42">
+      <c r="A40" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B40" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C40" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!C25</t>
+        </is>
+      </c>
+      <c r="D40" s="96" t="inlineStr">
+        <is>
+          <t>육지: 16일 63시간 30,725MWh 13.1억원 (3~6월). 제주: 표에 2023년까지만 수록</t>
+        </is>
+      </c>
+      <c r="E40" s="96" t="inlineStr">
+        <is>
+          <t>육지 2025: 16일 63시간 30,725MWh 13.1억 → 2026 3~6월: 26일 104시간 47,561MWh 21.6억 (전년 대비 1.7배). 제주: 2023 이후 표 미수록</t>
+        </is>
+      </c>
+      <c r="F40" s="96" t="inlineStr">
+        <is>
+          <t>2026 실적</t>
+        </is>
+      </c>
+      <c r="G40" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H40" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I40" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1" s="42">
+      <c r="A41" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B41" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C41" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!D25</t>
+        </is>
+      </c>
+      <c r="D41" s="96" t="inlineStr">
+        <is>
+          <t>자발적DR 연간 낙찰 15만MWh대, 신뢰성 감축시험 4,209~4,945MWh/회</t>
+        </is>
+      </c>
+      <c r="E41" s="96" t="inlineStr">
+        <is>
+          <t>자발적DR 2026 1~6월 낙찰 6,963~17,899MWh/월, 감축 10,735~25,612MWh/월. 미세먼지DR은 규칙 26-정기1차로 폐지</t>
+        </is>
+      </c>
+      <c r="F41" s="96" t="inlineStr">
+        <is>
+          <t>2026 실적·미세먼지DR 폐지</t>
+        </is>
+      </c>
+      <c r="G41" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H41" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I41" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1" s="42">
+      <c r="A42" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B42" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C42" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!A28</t>
+        </is>
+      </c>
+      <c r="D42" s="96" t="inlineStr">
+        <is>
+          <t>"2025년 단가" 행의 국민DR 평균 1,625원/kWh는 KPX 연간 정산금÷감축량으로 역산한 값(노랑)이다. 실제 고객이 받는 금액은 수요관리사업자가 이 정산금에서 운영비를 떼고 배분하므로 더 작다(사업자 계약</t>
+        </is>
+      </c>
+      <c r="E42" s="96" t="inlineStr">
+        <is>
+          <t>"단가" 행의 국민DR 평균(2025 1,625 / 2026 상반기 1,552원/kWh)는 KPX 연간 정산금÷감축량으로 역산한 값(노랑)이다. 실제 고객이 받는 금액은 수요관리사업자가 이 정산금에서 운영비를 떼고 배분하므로 더 작다(사업자 계약별, 공통값 없음). 2026년 RBP·M</t>
+        </is>
+      </c>
+      <c r="F42" s="96" t="inlineStr">
+        <is>
+          <t>주석 갱신</t>
+        </is>
+      </c>
+      <c r="G42" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H42" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I42" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1" s="42">
+      <c r="A43" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B43" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C43" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B41</t>
+        </is>
+      </c>
+      <c r="D43" s="96" t="inlineStr">
+        <is>
+          <t>2025년: 1,297,300천원 ÷ 798,187kWh ≈ 1,625원/kWh. 2025.12.17 18시 발령: 22,221kWh → 34,369천원(1,547원/kWh). 2025.12.29 11시: 13,03</t>
+        </is>
+      </c>
+      <c r="E43" s="96" t="inlineStr">
+        <is>
+          <t>2025년: 1,297,300천원 ÷ 798,187kWh ≈ 1,625원/kWh. 2026년 1~6월: 1,059,100천원 ÷ 682,625kWh ≈ 1,552원/kWh (RBP 인하 반영). 2026.6.29 19시 발령: 24,290kWh → 37,146천원(1,529원/kWh)</t>
+        </is>
+      </c>
+      <c r="F43" s="96" t="inlineStr">
+        <is>
+          <t>2026 실적 역산</t>
+        </is>
+      </c>
+      <c r="G43" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H43" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I43" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1" s="42">
+      <c r="A44" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B44" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C44" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B43</t>
+        </is>
+      </c>
+      <c r="D44" s="96" t="inlineStr">
+        <is>
+          <t>45시간 발령, 798,187kWh, 정산금 12.97억원. 참여고객 2025.12 85,011 → 2026.2 89,973 (12개 사업자, 214자원). 2020~2025 누적 304회·978MWh·16.1억원</t>
+        </is>
+      </c>
+      <c r="E44" s="96" t="inlineStr">
+        <is>
+          <t>2025: 45시간, 798,187kWh, 12.97억원. 2026 1~6월: 38시간, 682,625kWh, 10.59억원. 참여고객 2025.12 85,011 → 2026.2 89,973 → 2026.8 100,789 (12개 사업자, 218자원)</t>
+        </is>
+      </c>
+      <c r="F44" s="96" t="inlineStr">
+        <is>
+          <t>2026 실적·참여</t>
+        </is>
+      </c>
+      <c r="G44" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H44" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I44" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1" s="42">
+      <c r="A45" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B45" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C45" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!A52</t>
+        </is>
+      </c>
+      <c r="D45" s="96" t="inlineStr">
+        <is>
+          <t>정산 단가 (2025)</t>
+        </is>
+      </c>
+      <c r="E45" s="96" t="inlineStr">
+        <is>
+          <t>정산 단가 (2025 → 2026)</t>
+        </is>
+      </c>
+      <c r="F45" s="96" t="inlineStr">
+        <is>
+          <t>연도 갱신</t>
+        </is>
+      </c>
+      <c r="G45" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H45" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I45" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1" s="42">
+      <c r="A46" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B46" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C46" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B52</t>
+        </is>
+      </c>
+      <c r="D46" s="96" t="inlineStr">
+        <is>
+          <t>육지 50원/kWh (1~12월 동일), 제주 95~97원/kWh. 증대량 × 단가</t>
+        </is>
+      </c>
+      <c r="E46" s="96" t="inlineStr">
+        <is>
+          <t>육지 50원/kWh (2025 연중, 2026 평일). 2026.4.16부터 봄·가을철 공휴일·토요일 및 설·추석 연휴는 별표26 산식 61.35원/kWh(규칙 26-긴급4차). 제주 2025 95~97 → 2026.1~5월 96 → 6월 76원/kWh. 증대량 × 단가</t>
+        </is>
+      </c>
+      <c r="F46" s="96" t="inlineStr">
+        <is>
+          <t>휴일 61.35 신설</t>
+        </is>
+      </c>
+      <c r="G46" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H46" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I46" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1" s="42">
+      <c r="A47" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B47" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C47" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!A53</t>
+        </is>
+      </c>
+      <c r="D47" s="96" t="inlineStr">
+        <is>
+          <t>2025 실적</t>
+        </is>
+      </c>
+      <c r="E47" s="96" t="inlineStr">
+        <is>
+          <t>실적 (2025 → 2026 상반기)</t>
+        </is>
+      </c>
+      <c r="F47" s="96" t="inlineStr">
+        <is>
+          <t>연도 갱신</t>
+        </is>
+      </c>
+      <c r="G47" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H47" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I47" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1" s="42">
+      <c r="A48" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B48" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C48" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B53</t>
+        </is>
+      </c>
+      <c r="D48" s="96" t="inlineStr">
+        <is>
+          <t>육지: 3~6월 16일 63시간 30,725MWh, 정산금 13.1억원 (2024: 10일 21시간 7,187MWh 3.2억). 2025.7 이후·12월 실적 없음. 참여고객 육지 43,061 / 제주 1,573 (</t>
+        </is>
+      </c>
+      <c r="E48" s="96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">육지 2025: 3~6월 16일 63시간 30,725MWh 13.1억. 2026: 3월 4일13h 7,085MWh, 4월 7일33h 19,409MWh, 5월 10일42h 15,481MWh, 6월 5일16h 5,586MWh = 26일 104시간 47,561MWh 21.6억 (2026.6 </t>
+        </is>
+      </c>
+      <c r="F48" s="96" t="inlineStr">
+        <is>
+          <t>2026 실적</t>
+        </is>
+      </c>
+      <c r="G48" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H48" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I48" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1" s="42">
+      <c r="A49" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B49" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C49" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B67</t>
+        </is>
+      </c>
+      <c r="D49" s="96" t="inlineStr">
+        <is>
+          <t>수도권/비수도권 자원. RBP 67,277원/kW(2025)</t>
+        </is>
+      </c>
+      <c r="E49" s="96" t="inlineStr">
+        <is>
+          <t>수도권/비수도권 자원. RBP 65,760원/kW (2026, 2025는 67,277)</t>
+        </is>
+      </c>
+      <c r="F49" s="96" t="inlineStr">
+        <is>
+          <t>2026 단가</t>
+        </is>
+      </c>
+      <c r="G49" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H49" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I49" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1" s="42">
+      <c r="A50" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B50" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C50" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!C67</t>
+        </is>
+      </c>
+      <c r="D50" s="96" t="inlineStr">
+        <is>
+          <t>제주권 자원. RBP 76,562원/kW(2025) — 육지보다 14% 높음</t>
+        </is>
+      </c>
+      <c r="E50" s="96" t="inlineStr">
+        <is>
+          <t>제주권 자원. RBP 74,771원/kW (2026) — 육지보다 14% 높음</t>
+        </is>
+      </c>
+      <c r="F50" s="96" t="inlineStr">
+        <is>
+          <t>2026 단가</t>
+        </is>
+      </c>
+      <c r="G50" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H50" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I50" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1" s="42">
+      <c r="A51" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B51" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C51" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B68</t>
+        </is>
+      </c>
+      <c r="D51" s="96" t="inlineStr">
+        <is>
+          <t>2024.3.28 신설. 증대필요량 = 태양광이용률·수요구간 기준(KPX 매월 공지). 50원/kWh. 43,061고객</t>
+        </is>
+      </c>
+      <c r="E51" s="96" t="inlineStr">
+        <is>
+          <t>2024.3.28 신설. 증대필요량 = 태양광이용률·수요구간 기준(KPX 매월 공지). 평일 50원/kWh, 봄·가을 휴일·명절 61.35원/kWh(2026.4.16~). 42,651고객. 2026 상반기 104시간 발령</t>
+        </is>
+      </c>
+      <c r="F51" s="96" t="inlineStr">
+        <is>
+          <t>2026 반영</t>
+        </is>
+      </c>
+      <c r="G51" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H51" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I51" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1" s="42">
+      <c r="A52" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B52" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C52" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!C68</t>
+        </is>
+      </c>
+      <c r="D52" s="96" t="inlineStr">
+        <is>
+          <t>2021.1 신설, 2022.5 시장 분리. 출력제어량 기준 낙찰, 실시간(당일) 시장 병행. 95~97원/kWh. 1,573고객</t>
+        </is>
+      </c>
+      <c r="E52" s="96" t="inlineStr">
+        <is>
+          <t>2021.1 신설, 2022.5 시장 분리. 출력제어량 기준 낙찰, 실시간(당일) 시장 병행. 2026 96 → 6월 76원/kWh. 1,310고객</t>
+        </is>
+      </c>
+      <c r="F52" s="96" t="inlineStr">
+        <is>
+          <t>2026 반영</t>
+        </is>
+      </c>
+      <c r="G52" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H52" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I52" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1" s="42">
+      <c r="A53" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B53" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C53" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B70</t>
+        </is>
+      </c>
+      <c r="D53" s="96" t="inlineStr">
+        <is>
+          <t>국민DR + 플러스DR 둘 다 가능. 플러스DR 단가가 낮아 EV·ESS가 있어야 의미</t>
+        </is>
+      </c>
+      <c r="E53" s="96" t="inlineStr">
+        <is>
+          <t>국민DR + 플러스DR 둘 다 가능. 플러스DR은 2026년 봄·가을 주말 낮에 집중 발령(104시간)되고 휴일 단가 61.35원이라 EV·ESS 있는 가정은 주말 낮 충전 스케줄과 결합 가치 있음</t>
+        </is>
+      </c>
+      <c r="F53" s="96" t="inlineStr">
+        <is>
+          <t>2026 반영</t>
+        </is>
+      </c>
+      <c r="G53" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H53" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I53" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1" s="42">
+      <c r="A54" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B54" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C54" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B75</t>
+        </is>
+      </c>
+      <c r="D54" s="96" t="inlineStr">
+        <is>
+          <t>가정이 1시간에 1kWh 줄이면 KPX 정산 ≈ 1,600원(2025 평균). 연 45시간 전부 참여·매회 1kWh 감축 시 KPX 정산 ≈ 7만원, 사업자 배분 후 가정 수령은 그 일부. 감축량을 키우려면 히트펌프</t>
+        </is>
+      </c>
+      <c r="E54" s="96" t="inlineStr">
+        <is>
+          <t>가정이 1시간에 1kWh 줄이면 KPX 정산 ≈ 1,550~1,600원(2025 1,625 / 2026 상반기 1,552). 연 40~45시간 전부 참여·매회 1kWh 감축 시 KPX 정산 ≈ 6~7만원, 사업자 배분 후 가정 수령은 그 일부</t>
+        </is>
+      </c>
+      <c r="F54" s="96" t="inlineStr">
+        <is>
+          <t>2026 반영</t>
+        </is>
+      </c>
+      <c r="G54" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H54" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I54" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1" s="42">
+      <c r="A55" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B55" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C55" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B76</t>
+        </is>
+      </c>
+      <c r="D55" s="96" t="inlineStr">
+        <is>
+          <t>EV 30kWh 충전을 잉여 시간으로 옮기면 육지 50원 × 30 = 1,500원/회, 제주 96원 × 30 = 2,880원/회 (KPX 정산 기준). 2025 육지 발령 63시간이므로 연 수만 원 규모. 요금 측면</t>
+        </is>
+      </c>
+      <c r="E55" s="96" t="inlineStr">
+        <is>
+          <t>EV 30kWh 충전을 잉여 시간으로 옮기면 육지 평일 50원 × 30 = 1,500원/회, 봄·가을 휴일 61.35 × 30 = 1,841원/회, 제주 76~96원 × 30 = 2,280~2,880원/회 (KPX 정산 기준). 2026 상반기 육지 발령 104시간이므로 연 수만 원 규</t>
+        </is>
+      </c>
+      <c r="F55" s="96" t="inlineStr">
+        <is>
+          <t>2026 반영</t>
+        </is>
+      </c>
+      <c r="G55" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H55" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I55" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1" s="42">
+      <c r="A56" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B56" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C56" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!B78</t>
+        </is>
+      </c>
+      <c r="D56" s="96" t="inlineStr">
+        <is>
+          <t>2026년 RBP·MRT·플러스DR 단가(KPX 월간 현황 보고서), 사업자별 고객 배분율·보상 방식, 국민DR 일일 발령 한도·기온 기준 조항 개정 여부, 제주 플러스DR 2024~2025 실적(보고서 표 미수록)</t>
+        </is>
+      </c>
+      <c r="E56" s="96" t="inlineStr">
+        <is>
+          <t>2026 하반기 RBP·MRT(KPX 월간 현황 보고서로 매월 갱신), 사업자별 고객 배분율·보상 방식, 제주 플러스DR 2024~2026 실적(보고서 표 미수록), 61.35원 적용 산식(별표26) 원문</t>
+        </is>
+      </c>
+      <c r="F56" s="96" t="inlineStr">
+        <is>
+          <t>갱신</t>
+        </is>
+      </c>
+      <c r="G56" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H56" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I56" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1" s="42">
+      <c r="A57" s="95" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="B57" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C57" s="96" t="inlineStr">
+        <is>
+          <t>DR_수요반응!A80:E98</t>
+        </is>
+      </c>
+      <c r="D57" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="96" t="inlineStr">
+        <is>
+          <t>H절 현황판 키값 17행 신설</t>
+        </is>
+      </c>
+      <c r="F57" s="96" t="inlineStr">
+        <is>
+          <t>현황판이 엑셀에서 DR 숫자를 읽도록</t>
+        </is>
+      </c>
+      <c r="G57" s="96" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H57" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I57" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/한전_전기요금_2026_HEMS정리.xlsx
+++ b/data/한전_전기요금_2026_HEMS정리.xlsx
@@ -1082,6 +1082,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="17.15" customHeight="1" s="42">
       <c r="A4" s="45" t="inlineStr">
         <is>
@@ -1096,6 +1097,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="30" customHeight="1" s="42">
       <c r="A7" s="47" t="inlineStr">
         <is>
@@ -1576,6 +1578,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="17.15" customHeight="1" s="42">
       <c r="A23" s="45" t="inlineStr">
         <is>
@@ -1775,6 +1778,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="17.15" customHeight="1" s="42">
       <c r="A31" s="45" t="inlineStr">
         <is>
@@ -2150,6 +2154,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45" ht="55.5" customHeight="1" s="42">
       <c r="A45" s="55" t="inlineStr">
         <is>
@@ -2257,6 +2262,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="42">
       <c r="A4" s="47" t="inlineStr">
         <is>
@@ -2622,6 +2628,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="42">
       <c r="A4" s="47" t="inlineStr">
         <is>
@@ -2840,6 +2847,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="17.15" customHeight="1" s="42">
       <c r="A13" s="61" t="inlineStr">
         <is>
@@ -3023,6 +3031,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1" s="42">
       <c r="A4" s="92" t="inlineStr">
         <is>
@@ -3258,6 +3267,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="20" customHeight="1" s="42">
       <c r="A12" s="92" t="inlineStr">
         <is>
@@ -4053,6 +4063,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="20" customHeight="1" s="42">
       <c r="A30" s="92" t="inlineStr">
         <is>
@@ -4383,6 +4394,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46" ht="20" customHeight="1" s="42">
       <c r="A46" s="92" t="inlineStr">
         <is>
@@ -4603,6 +4615,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57" ht="20" customHeight="1" s="42">
       <c r="A57" s="92" t="inlineStr">
         <is>
@@ -4757,6 +4770,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65" ht="20" customHeight="1" s="42">
       <c r="A65" s="92" t="inlineStr">
         <is>
@@ -4889,6 +4903,7 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
     <row r="72" ht="20" customHeight="1" s="42">
       <c r="A72" s="92" t="inlineStr">
         <is>
@@ -5043,21 +5058,22 @@
         </is>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="92" t="inlineStr">
         <is>
           <t>H. 현황판 키값 (scripts/extract.py가 읽어 현황판에 표시 — 키 이름 변경 금지, 값만 갱신)</t>
         </is>
       </c>
-      <c r="B80" s="93" t="n"/>
-      <c r="C80" s="93" t="n"/>
-      <c r="D80" s="93" t="n"/>
-      <c r="E80" s="93" t="n"/>
-      <c r="F80" s="93" t="n"/>
-      <c r="G80" s="93" t="n"/>
-      <c r="H80" s="93" t="n"/>
-      <c r="I80" s="93" t="n"/>
-      <c r="J80" s="93" t="n"/>
+      <c r="B80" s="70" t="n"/>
+      <c r="C80" s="70" t="n"/>
+      <c r="D80" s="70" t="n"/>
+      <c r="E80" s="70" t="n"/>
+      <c r="F80" s="70" t="n"/>
+      <c r="G80" s="70" t="n"/>
+      <c r="H80" s="70" t="n"/>
+      <c r="I80" s="70" t="n"/>
+      <c r="J80" s="71" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="104" t="inlineStr">
@@ -5568,6 +5584,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="17.15" customHeight="1" s="42">
       <c r="A4" s="61" t="inlineStr">
         <is>
@@ -5710,6 +5727,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="17.15" customHeight="1" s="42">
       <c r="A11" s="61" t="inlineStr">
         <is>
@@ -5845,6 +5863,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="17.15" customHeight="1" s="42">
       <c r="A17" s="61" t="inlineStr">
         <is>
@@ -5977,6 +5996,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="42">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -7368,7 +7388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="42" min="1" max="1"/>
@@ -7395,7 +7415,7 @@
       </c>
       <c r="C1" s="101" t="inlineStr">
         <is>
-          <t>v13</t>
+          <t>v14</t>
         </is>
       </c>
       <c r="D1" s="91" t="inlineStr">
@@ -7416,6 +7436,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1" s="42">
       <c r="A4" s="94" t="inlineStr">
         <is>
@@ -9373,6 +9394,51 @@
         </is>
       </c>
       <c r="I57" s="96" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1" s="42">
+      <c r="A58" s="95" t="inlineStr">
+        <is>
+          <t>v14</t>
+        </is>
+      </c>
+      <c r="B58" s="96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C58" s="96" t="inlineStr">
+        <is>
+          <t>주택용!B32:D33 등 수식 12개</t>
+        </is>
+      </c>
+      <c r="D58" s="96">
+        <f>B24*요금구성_공통!$C$5</f>
+        <v/>
+      </c>
+      <c r="E58" s="96">
+        <f>B24*'요금구성_공통'!$C$5</f>
+        <v/>
+      </c>
+      <c r="F58" s="96" t="inlineStr">
+        <is>
+          <t>Excel이 한글 시트명 참조를 따옴표 없이는 인식하지 못해 "수식 제거" 복구 경고 발생 → 시트명에 작은따옴표. 값 변경 없음</t>
+        </is>
+      </c>
+      <c r="G58" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="96" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I58" s="96" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
@@ -9419,6 +9485,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1" s="42">
       <c r="A4" s="92" t="inlineStr">
         <is>
@@ -9706,6 +9773,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="20" customHeight="1" s="42">
       <c r="A16" s="92" t="inlineStr">
         <is>
@@ -10273,6 +10341,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="20" customHeight="1" s="42">
       <c r="A32" s="92" t="inlineStr">
         <is>
@@ -10432,6 +10501,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="20" customHeight="1" s="42">
       <c r="A40" s="92" t="inlineStr">
         <is>
@@ -10560,6 +10630,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47" ht="20" customHeight="1" s="42">
       <c r="A47" s="92" t="inlineStr">
         <is>
@@ -12371,6 +12442,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="72" customHeight="1" s="42">
       <c r="A16" s="46" t="inlineStr">
         <is>
@@ -12428,6 +12500,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="17.15" customHeight="1" s="42">
       <c r="A4" s="61" t="inlineStr">
         <is>
@@ -12944,6 +13017,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="17.15" customHeight="1" s="42">
       <c r="A22" s="61" t="inlineStr">
         <is>
@@ -13142,15 +13216,15 @@
         </is>
       </c>
       <c r="B32" s="68">
-        <f>B24*요금구성_공통!$C$5</f>
+        <f>B24*'요금구성_공통'!$C$5</f>
         <v/>
       </c>
       <c r="C32" s="68">
-        <f>C24*요금구성_공통!$C$5</f>
+        <f>C24*'요금구성_공통'!$C$5</f>
         <v/>
       </c>
       <c r="D32" s="68">
-        <f>D24*요금구성_공통!$C$5</f>
+        <f>D24*'요금구성_공통'!$C$5</f>
         <v/>
       </c>
     </row>
@@ -13161,15 +13235,15 @@
         </is>
       </c>
       <c r="B33" s="68">
-        <f>B24*요금구성_공통!$C$6</f>
+        <f>B24*'요금구성_공통'!$C$6</f>
         <v/>
       </c>
       <c r="C33" s="68">
-        <f>C24*요금구성_공통!$C$6</f>
+        <f>C24*'요금구성_공통'!$C$6</f>
         <v/>
       </c>
       <c r="D33" s="68">
-        <f>D24*요금구성_공통!$C$6</f>
+        <f>D24*'요금구성_공통'!$C$6</f>
         <v/>
       </c>
     </row>
@@ -13199,15 +13273,15 @@
         </is>
       </c>
       <c r="B35" s="68">
-        <f>B34*요금구성_공통!$C$7</f>
+        <f>B34*'요금구성_공통'!$C$7</f>
         <v/>
       </c>
       <c r="C35" s="68">
-        <f>C34*요금구성_공통!$C$7</f>
+        <f>C34*'요금구성_공통'!$C$7</f>
         <v/>
       </c>
       <c r="D35" s="68">
-        <f>D34*요금구성_공통!$C$7</f>
+        <f>D34*'요금구성_공통'!$C$7</f>
         <v/>
       </c>
     </row>
@@ -13218,15 +13292,15 @@
         </is>
       </c>
       <c r="B36" s="68">
-        <f>B34*요금구성_공통!$C$8</f>
+        <f>B34*'요금구성_공통'!$C$8</f>
         <v/>
       </c>
       <c r="C36" s="68">
-        <f>C34*요금구성_공통!$C$8</f>
+        <f>C34*'요금구성_공통'!$C$8</f>
         <v/>
       </c>
       <c r="D36" s="68">
-        <f>D34*요금구성_공통!$C$8</f>
+        <f>D34*'요금구성_공통'!$C$8</f>
         <v/>
       </c>
     </row>
@@ -13261,6 +13335,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="17.15" customHeight="1" s="42">
       <c r="A40" s="61" t="inlineStr">
         <is>
@@ -13437,6 +13512,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48" ht="17.15" customHeight="1" s="42">
       <c r="A48" s="61" t="inlineStr">
         <is>
@@ -13587,6 +13663,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55" ht="17.15" customHeight="1" s="42">
       <c r="A55" s="61" t="inlineStr">
         <is>
@@ -13774,6 +13851,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="42">
       <c r="A4" s="47" t="inlineStr">
         <is>
@@ -13901,6 +13979,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="43.5" customHeight="1" s="42">
       <c r="A10" s="60" t="inlineStr">
         <is>
@@ -13952,6 +14031,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="42">
       <c r="A4" s="47" t="inlineStr">
         <is>
@@ -15889,6 +15969,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="17.15" customHeight="1" s="42">
       <c r="A4" s="45" t="inlineStr">
         <is>
@@ -15973,6 +16054,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="30" customHeight="1" s="42">
       <c r="A11" s="47" t="inlineStr">
         <is>
@@ -18303,6 +18385,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="42">
       <c r="A4" s="47" t="inlineStr">
         <is>
